--- a/python/zombie/planilla.xlsx
+++ b/python/zombie/planilla.xlsx
@@ -54,11 +54,4 @@
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=zombie_infection/.zombie_marker.txt>ZOMBIE VIRUS - INFECTION MARKER
-Timestamp: 2026-07-10 13:41:51.625554
-Original file: planilla.xlsx
-This file was infected by the Zombie educational virus.
-
 </file>
--- a/python/zombie/planilla.xlsx
+++ b/python/zombie/planilla.xlsx
@@ -54,4 +54,11 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=zombie_infection/.zombie_marker.txt>ZOMBIE VIRUS - MARCADOR DE INFECCION
+Timestamp: 2026-07-10 14:04:06.817265
+Archivo original: planilla.xlsx
+Este archivo fue infectado por el virus educativo Zombie.
+
 </file>